--- a/spain_dwelling_types.xlsx
+++ b/spain_dwelling_types.xlsx
@@ -1,18 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thomashunn/Downloads/NTNU/NTNU2/MFA2/SPN_Project_fix/MFA2/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAEF024-CF6F-2640-8EA6-5A95315FA61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sources (APA 7th)" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sources (APA 7th)" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -23,176 +39,173 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="54">
   <si>
-    <t xml:space="preserve">Spain: Dwelling Type Split (1600–2024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of population by dwelling type  |  % of total dwellings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apartment / Flat (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semi-Detached / Terraced (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detached (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Quality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source / Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extrapolated from urbanisation rates. Spain ~85% rural. Apartments confined to Madrid &amp; Seville cores.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minor urban growth. Rural detached dominant. Pre-Bourbon demographic stagnation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urban share ~10%. Madrid established as capital; limited tenement growth.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bourbon reforms stimulate modest urban expansion. Barcelona growing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War of Independence disrupts urbanisation. Urban share ~12%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Early industrialisation. Catalonia textile boom. Urban share ~16%. Cerdà designing Eixample.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INE building census: avg floors/building = 1.65. Urban share ~32%. Rural exodus beginning.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interpolated from 1900 census and 1930 trends.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interpolated. Early 20th-c urbanisation accelerating.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INE data: avg floors/building = 1.72. Population ~24m. Urban ~35%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post Civil War. Autarky slows construction. Urban share ~40%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Census</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INE Censo de Edificios y Viviendas 1950. Rural exodus beginning under Franco industrialisation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INE census. Mass internal migration. State high-rise housing programme (Ministerio de la Vivienda).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INE Censo de Edificios y Viviendas 1970. Peak apartment construction decade (H-block era).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INE Census 1981. Rural exodus slowing. Urban share ~73%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INE Census 1991. Urban sprawl and townhouse developments emerge.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INE Census 2001 / Atlas de la Edificación Residencial: 33.2% single-family, 66.8% multi-unit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurostat EU-SILC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurostat ilc_lvho01. Annual survey begins.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurostat ilc_lvho01.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurostat ilc_lvho01. Post-housing bubble collapse.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurostat ilc_lvho01. Post-COVID uptick in detached demand noted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurostat ilc_lvho01. Spain highest apartment share in EU.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Quality Legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extrapolated from urbanisation statistics, architectural history, and economic demography. Treat as indicative only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INE (Instituto Nacional de Estadística) decennial census of buildings and dwellings.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annual survey (ilc_lvho01). Most reliable series. Covers % of population by dwelling type.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sources — APA 7th Edition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary — Eurostat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurostat. (2025). Distribution of population by degree of urbanisation, dwelling type and income group [Data set]. European Commission. https://ec.europa.eu/eurostat/databrowser/view/ilc_lvho01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary — INE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instituto Nacional de Estadística. (2001). Atlas de la edificación residencial en España. Ministerio de Transportes, Movilidad y Agenda Urbana. https://www.mitma.gob.es</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instituto Nacional de Estadística. (1970). Censo de edificios y viviendas 1970. INE.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instituto Nacional de Estadística. (1950). Censo de edificios y viviendas 1950. INE.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secondary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sánchez, R., &amp; Plaza, A. (n.d.). Spain lives in flats: Why we have built our cities vertically. elDiario.es. https://especiales.eldiario.es/spain-lives-in-flats/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historical est.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carmona, J., &amp; Rosés, J. R. (2012). Land markets and agrarian backwardness (Spain, 1904–1934). European Review of Economic History, 16(1), 74–96. https://doi.org/10.1093/ereh/her017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reher, D. S. (1990). Town and country in pre-industrial Spain: Cuenca, 1550–1870. Cambridge University Press.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-1900 figures are estimates extrapolated from urbanisation rates and historical demography. They do not derive from direct dwelling-type surveys and should be treated as indicative only.</t>
+    <t>Spain: Dwelling Type Split (1600–2024)</t>
+  </si>
+  <si>
+    <t>Share of population by dwelling type  |  % of total dwellings</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Apartment / Flat (%)</t>
+  </si>
+  <si>
+    <t>Semi-Detached / Terraced (%)</t>
+  </si>
+  <si>
+    <t>Detached (%)</t>
+  </si>
+  <si>
+    <t>Total (%)</t>
+  </si>
+  <si>
+    <t>Data Quality</t>
+  </si>
+  <si>
+    <t>Source / Notes</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>Extrapolated from urbanisation rates. Spain ~85% rural. Apartments confined to Madrid &amp; Seville cores.</t>
+  </si>
+  <si>
+    <t>Minor urban growth. Rural detached dominant. Pre-Bourbon demographic stagnation.</t>
+  </si>
+  <si>
+    <t>Urban share ~10%. Madrid established as capital; limited tenement growth.</t>
+  </si>
+  <si>
+    <t>Bourbon reforms stimulate modest urban expansion. Barcelona growing.</t>
+  </si>
+  <si>
+    <t>War of Independence disrupts urbanisation. Urban share ~12%.</t>
+  </si>
+  <si>
+    <t>Early industrialisation. Catalonia textile boom. Urban share ~16%. Cerdà designing Eixample.</t>
+  </si>
+  <si>
+    <t>INE building census: avg floors/building = 1.65. Urban share ~32%. Rural exodus beginning.</t>
+  </si>
+  <si>
+    <t>Interpolated from 1900 census and 1930 trends.</t>
+  </si>
+  <si>
+    <t>Interpolated. Early 20th-c urbanisation accelerating.</t>
+  </si>
+  <si>
+    <t>INE data: avg floors/building = 1.72. Population ~24m. Urban ~35%.</t>
+  </si>
+  <si>
+    <t>Post Civil War. Autarky slows construction. Urban share ~40%.</t>
+  </si>
+  <si>
+    <t>Census</t>
+  </si>
+  <si>
+    <t>INE Censo de Edificios y Viviendas 1950. Rural exodus beginning under Franco industrialisation.</t>
+  </si>
+  <si>
+    <t>INE census. Mass internal migration. State high-rise housing programme (Ministerio de la Vivienda).</t>
+  </si>
+  <si>
+    <t>INE Censo de Edificios y Viviendas 1970. Peak apartment construction decade (H-block era).</t>
+  </si>
+  <si>
+    <t>INE Census 1981. Rural exodus slowing. Urban share ~73%.</t>
+  </si>
+  <si>
+    <t>INE Census 1991. Urban sprawl and townhouse developments emerge.</t>
+  </si>
+  <si>
+    <t>INE Census 2001 / Atlas de la Edificación Residencial: 33.2% single-family, 66.8% multi-unit.</t>
+  </si>
+  <si>
+    <t>Eurostat EU-SILC</t>
+  </si>
+  <si>
+    <t>Eurostat ilc_lvho01. Annual survey begins.</t>
+  </si>
+  <si>
+    <t>Eurostat ilc_lvho01.</t>
+  </si>
+  <si>
+    <t>Eurostat ilc_lvho01. Post-housing bubble collapse.</t>
+  </si>
+  <si>
+    <t>Eurostat ilc_lvho01. Post-COVID uptick in detached demand noted.</t>
+  </si>
+  <si>
+    <t>Eurostat ilc_lvho01. Spain highest apartment share in EU.</t>
+  </si>
+  <si>
+    <t>Data Quality Legend</t>
+  </si>
+  <si>
+    <t>Extrapolated from urbanisation statistics, architectural history, and economic demography. Treat as indicative only.</t>
+  </si>
+  <si>
+    <t>INE (Instituto Nacional de Estadística) decennial census of buildings and dwellings.</t>
+  </si>
+  <si>
+    <t>Annual survey (ilc_lvho01). Most reliable series. Covers % of population by dwelling type.</t>
+  </si>
+  <si>
+    <t>Sources — APA 7th Edition</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Primary — Eurostat</t>
+  </si>
+  <si>
+    <t>Eurostat. (2025). Distribution of population by degree of urbanisation, dwelling type and income group [Data set]. European Commission. https://ec.europa.eu/eurostat/databrowser/view/ilc_lvho01</t>
+  </si>
+  <si>
+    <t>Primary — INE</t>
+  </si>
+  <si>
+    <t>Instituto Nacional de Estadística. (2001). Atlas de la edificación residencial en España. Ministerio de Transportes, Movilidad y Agenda Urbana. https://www.mitma.gob.es</t>
+  </si>
+  <si>
+    <t>Instituto Nacional de Estadística. (1970). Censo de edificios y viviendas 1970. INE.</t>
+  </si>
+  <si>
+    <t>Instituto Nacional de Estadística. (1950). Censo de edificios y viviendas 1950. INE.</t>
+  </si>
+  <si>
+    <t>Secondary</t>
+  </si>
+  <si>
+    <t>Sánchez, R., &amp; Plaza, A. (n.d.). Spain lives in flats: Why we have built our cities vertically. elDiario.es. https://especiales.eldiario.es/spain-lives-in-flats/</t>
+  </si>
+  <si>
+    <t>Historical est.</t>
+  </si>
+  <si>
+    <t>Carmona, J., &amp; Rosés, J. R. (2012). Land markets and agrarian backwardness (Spain, 1904–1934). European Review of Economic History, 16(1), 74–96. https://doi.org/10.1093/ereh/her017</t>
+  </si>
+  <si>
+    <t>Reher, D. S. (1990). Town and country in pre-industrial Spain: Cuenca, 1550–1870. Cambridge University Press.</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Pre-1900 figures are estimates extrapolated from urbanisation rates and historical demography. They do not derive from direct dwelling-type surveys and should be treated as indicative only.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,71 +214,49 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -307,14 +298,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -330,113 +321,68 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -495,47 +441,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2F5496"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -543,12 +505,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -577,7 +539,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -598,7 +560,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -649,7 +611,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -667,871 +629,862 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="52"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="7">
         <v>1600</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="7">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="7">
         <v>5</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="7">
         <v>92</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <f aca="false">B4+C4+D4</f>
-        <v>100</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="E4" s="7">
+        <f t="shared" ref="E4:E32" si="0">B4+C4+D4</f>
+        <v>100</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7">
         <v>1650</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="7">
         <v>3.5</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="7">
         <v>5.5</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="7">
         <v>91</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <f aca="false">B5+C5+D5</f>
-        <v>100</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="E5" s="7">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7">
         <v>1700</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="7">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="7">
         <v>6</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="7">
         <v>90</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <f aca="false">B6+C6+D6</f>
-        <v>100</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="E6" s="7">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
         <v>1750</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="7">
         <v>4.5</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="7">
         <v>6.5</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="7">
         <v>89</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <f aca="false">B7+C7+D7</f>
-        <v>100</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="E7" s="7">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7">
         <v>1800</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="7">
         <v>5.5</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="7">
         <v>7.5</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="7">
         <v>87</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <f aca="false">B8+C8+D8</f>
-        <v>100</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="E8" s="7">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="7">
         <v>1850</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="7">
         <v>7</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="7">
         <v>8</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="7">
         <v>85</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <f aca="false">B9+C9+D9</f>
-        <v>100</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="E9" s="7">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="7">
         <v>1900</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7">
         <v>10</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="7">
         <v>8</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="7">
         <v>82</v>
       </c>
-      <c r="E10" s="4" t="n">
-        <f aca="false">B10+C10+D10</f>
-        <v>100</v>
-      </c>
-      <c r="F10" s="5" t="s">
+      <c r="E10" s="7">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="7">
         <v>1910</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7">
         <v>11</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="7">
         <v>9</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="7">
         <v>80</v>
       </c>
-      <c r="E11" s="4" t="n">
-        <f aca="false">B11+C11+D11</f>
-        <v>100</v>
-      </c>
-      <c r="F11" s="5" t="s">
+      <c r="E11" s="7">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="7">
         <v>1920</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="7">
         <v>13</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="7">
         <v>10</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="7">
         <v>77</v>
       </c>
-      <c r="E12" s="4" t="n">
-        <f aca="false">B12+C12+D12</f>
-        <v>100</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="E12" s="7">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="7">
         <v>1930</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="7">
         <v>16</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="7">
         <v>11</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="7">
         <v>73</v>
       </c>
-      <c r="E13" s="4" t="n">
-        <f aca="false">B13+C13+D13</f>
-        <v>100</v>
-      </c>
-      <c r="F13" s="5" t="s">
+      <c r="E13" s="7">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="7">
         <v>1940</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="7">
         <v>20</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="7">
         <v>12</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="7">
         <v>68</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <f aca="false">B14+C14+D14</f>
-        <v>100</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="E14" s="7">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="9">
         <v>1950</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="9">
         <v>28</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="9">
         <v>13</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="9">
         <v>59</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <f aca="false">B15+C15+D15</f>
-        <v>100</v>
-      </c>
-      <c r="F15" s="7" t="s">
+      <c r="E15" s="9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F15" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="9">
         <v>1960</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="9">
         <v>38</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="9">
         <v>14</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="9">
         <v>48</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <f aca="false">B16+C16+D16</f>
-        <v>100</v>
-      </c>
-      <c r="F16" s="7" t="s">
+      <c r="E16" s="9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="9">
         <v>1970</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="9">
         <v>50</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="9">
         <v>15</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="9">
         <v>35</v>
       </c>
-      <c r="E17" s="6" t="n">
-        <f aca="false">B17+C17+D17</f>
-        <v>100</v>
-      </c>
-      <c r="F17" s="7" t="s">
+      <c r="E17" s="9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="n">
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="9">
         <v>1981</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="9">
         <v>55</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="9">
         <v>17</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="9">
         <v>28</v>
       </c>
-      <c r="E18" s="6" t="n">
-        <f aca="false">B18+C18+D18</f>
-        <v>100</v>
-      </c>
-      <c r="F18" s="7" t="s">
+      <c r="E18" s="9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F18" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="n">
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="9">
         <v>1991</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="9">
         <v>59</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="9">
         <v>19</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="9">
         <v>22</v>
       </c>
-      <c r="E19" s="6" t="n">
-        <f aca="false">B19+C19+D19</f>
-        <v>100</v>
-      </c>
-      <c r="F19" s="7" t="s">
+      <c r="E19" s="9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F19" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="n">
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="9">
         <v>2001</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="9">
         <v>63</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="9">
         <v>21</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="9">
         <v>16</v>
       </c>
-      <c r="E20" s="6" t="n">
-        <f aca="false">B20+C20+D20</f>
-        <v>100</v>
-      </c>
-      <c r="F20" s="7" t="s">
+      <c r="E20" s="9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F20" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="n">
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="11">
         <v>2003</v>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="11">
         <v>63.5</v>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="11">
         <v>20.5</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="11">
         <v>16</v>
       </c>
-      <c r="E21" s="8" t="n">
-        <f aca="false">B21+C21+D21</f>
-        <v>100</v>
-      </c>
-      <c r="F21" s="9" t="s">
+      <c r="E21" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F21" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="n">
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="11">
         <v>2005</v>
       </c>
-      <c r="B22" s="8" t="n">
+      <c r="B22" s="11">
         <v>63.5</v>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="11">
         <v>20.5</v>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="11">
         <v>16</v>
       </c>
-      <c r="E22" s="8" t="n">
-        <f aca="false">B22+C22+D22</f>
-        <v>100</v>
-      </c>
-      <c r="F22" s="9" t="s">
+      <c r="E22" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F22" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="n">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="11">
         <v>2008</v>
       </c>
-      <c r="B23" s="8" t="n">
-        <v>64.4</v>
-      </c>
-      <c r="C23" s="8" t="n">
+      <c r="B23" s="11">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="C23" s="11">
         <v>22.5</v>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="11">
         <v>13.1</v>
       </c>
-      <c r="E23" s="8" t="n">
-        <f aca="false">B23+C23+D23</f>
-        <v>100</v>
-      </c>
-      <c r="F23" s="9" t="s">
+      <c r="E23" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F23" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="n">
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="11">
         <v>2010</v>
       </c>
-      <c r="B24" s="8" t="n">
+      <c r="B24" s="11">
         <v>64.5</v>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="11">
         <v>22.5</v>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="11">
         <v>13</v>
       </c>
-      <c r="E24" s="8" t="n">
-        <f aca="false">B24+C24+D24</f>
-        <v>100</v>
-      </c>
-      <c r="F24" s="9" t="s">
+      <c r="E24" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F24" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="n">
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="11">
         <v>2012</v>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B25" s="11">
         <v>65</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="11">
         <v>21.5</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="11">
         <v>13.5</v>
       </c>
-      <c r="E25" s="8" t="n">
-        <f aca="false">B25+C25+D25</f>
-        <v>100</v>
-      </c>
-      <c r="F25" s="9" t="s">
+      <c r="E25" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F25" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="n">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="11">
         <v>2015</v>
       </c>
-      <c r="B26" s="8" t="n">
+      <c r="B26" s="11">
         <v>65</v>
       </c>
-      <c r="C26" s="8" t="n">
+      <c r="C26" s="11">
         <v>20</v>
       </c>
-      <c r="D26" s="8" t="n">
+      <c r="D26" s="11">
         <v>15</v>
       </c>
-      <c r="E26" s="8" t="n">
-        <f aca="false">B26+C26+D26</f>
-        <v>100</v>
-      </c>
-      <c r="F26" s="9" t="s">
+      <c r="E26" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F26" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="n">
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="11">
         <v>2016</v>
       </c>
-      <c r="B27" s="8" t="n">
-        <v>65.1</v>
-      </c>
-      <c r="C27" s="8" t="n">
+      <c r="B27" s="11">
+        <v>65.099999999999994</v>
+      </c>
+      <c r="C27" s="11">
         <v>21.5</v>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="11">
         <v>12</v>
       </c>
-      <c r="E27" s="8" t="n">
-        <f aca="false">B27+C27+D27</f>
+      <c r="E27" s="11">
+        <f t="shared" si="0"/>
         <v>98.6</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="n">
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="11">
         <v>2019</v>
       </c>
-      <c r="B28" s="8" t="n">
+      <c r="B28" s="11">
         <v>65</v>
       </c>
-      <c r="C28" s="8" t="n">
+      <c r="C28" s="11">
         <v>21</v>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="D28" s="11">
         <v>14</v>
       </c>
-      <c r="E28" s="8" t="n">
-        <f aca="false">B28+C28+D28</f>
-        <v>100</v>
-      </c>
-      <c r="F28" s="9" t="s">
+      <c r="E28" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F28" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="n">
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="11">
         <v>2020</v>
       </c>
-      <c r="B29" s="8" t="n">
+      <c r="B29" s="11">
         <v>65.5</v>
       </c>
-      <c r="C29" s="8" t="n">
+      <c r="C29" s="11">
         <v>19.5</v>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="11">
         <v>15</v>
       </c>
-      <c r="E29" s="8" t="n">
-        <f aca="false">B29+C29+D29</f>
-        <v>100</v>
-      </c>
-      <c r="F29" s="9" t="s">
+      <c r="E29" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F29" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="n">
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="11">
         <v>2022</v>
       </c>
-      <c r="B30" s="8" t="n">
+      <c r="B30" s="11">
         <v>66</v>
       </c>
-      <c r="C30" s="8" t="n">
+      <c r="C30" s="11">
         <v>17.5</v>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="D30" s="11">
         <v>16.5</v>
       </c>
-      <c r="E30" s="8" t="n">
-        <f aca="false">B30+C30+D30</f>
-        <v>100</v>
-      </c>
-      <c r="F30" s="9" t="s">
+      <c r="E30" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F30" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="n">
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="11">
         <v>2023</v>
       </c>
-      <c r="B31" s="8" t="n">
+      <c r="B31" s="11">
         <v>66</v>
       </c>
-      <c r="C31" s="8" t="n">
+      <c r="C31" s="11">
         <v>17.5</v>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="11">
         <v>16.5</v>
       </c>
-      <c r="E31" s="8" t="n">
-        <f aca="false">B31+C31+D31</f>
-        <v>100</v>
-      </c>
-      <c r="F31" s="9" t="s">
+      <c r="E31" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F31" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="n">
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="11">
         <v>2024</v>
       </c>
-      <c r="B32" s="8" t="n">
+      <c r="B32" s="11">
         <v>66</v>
       </c>
-      <c r="C32" s="8" t="n">
+      <c r="C32" s="11">
         <v>17</v>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="11">
         <v>17</v>
       </c>
-      <c r="E32" s="8" t="n">
-        <f aca="false">B32+C32+D32</f>
-        <v>100</v>
-      </c>
-      <c r="F32" s="9" t="s">
+      <c r="E32" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F32" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11"/>
-      <c r="B35" s="10" t="s">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="13"/>
+      <c r="B35" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="12" t="s">
+      <c r="C35" s="3"/>
+      <c r="D35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13"/>
-      <c r="B36" s="10" t="s">
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="14"/>
+      <c r="B36" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="12" t="s">
+      <c r="C36" s="3"/>
+      <c r="D36" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14"/>
-      <c r="B37" s="10" t="s">
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="15"/>
+      <c r="B37" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="12" t="s">
+      <c r="C37" s="3"/>
+      <c r="D37" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:G37"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A34:G34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="D35:G35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:G37"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="110"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="15"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
         <v>41</v>
       </c>
@@ -1539,7 +1492,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
         <v>43</v>
       </c>
@@ -1547,7 +1500,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
         <v>43</v>
       </c>
@@ -1555,7 +1508,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
         <v>43</v>
       </c>
@@ -1563,7 +1516,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
         <v>47</v>
       </c>
@@ -1571,7 +1524,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="16" t="s">
         <v>49</v>
       </c>
@@ -1579,7 +1532,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
         <v>49</v>
       </c>
@@ -1587,7 +1540,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
         <v>52</v>
       </c>
@@ -1599,12 +1552,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>